--- a/Output/PowerPoint_Figures/Fig_3/Fig_3b_Mexiletine_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3b_Mexiletine_data.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,183 +420,183 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>24</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>40</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>42</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>45</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>48</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>50</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>53</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>55</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>58</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>61</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>63</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>66</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>69</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>71</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>74</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>77</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>79</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>82</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>85</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>87</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>90</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>93</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.91864542252362</v>
+        <v>38.45932271126182</v>
       </c>
       <c r="C2" t="n">
-        <v>48.3876388030114</v>
+        <v>41.49227425188206</v>
       </c>
       <c r="D2" t="n">
-        <v>49.84443670510836</v>
+        <v>44.88332752883116</v>
       </c>
       <c r="E2" t="n">
-        <v>51.28199142634407</v>
+        <v>48.62174249805096</v>
       </c>
       <c r="F2" t="n">
-        <v>52.69107403705785</v>
+        <v>52.69107403705774</v>
       </c>
       <c r="G2" t="n">
-        <v>54.07245976495426</v>
+        <v>54.07245976495412</v>
       </c>
       <c r="H2" t="n">
-        <v>55.44140269441648</v>
+        <v>55.44140269441637</v>
       </c>
       <c r="I2" t="n">
-        <v>56.85555138129186</v>
+        <v>56.85555138129177</v>
       </c>
       <c r="J2" t="n">
-        <v>58.27606612056277</v>
+        <v>58.27606612056267</v>
       </c>
       <c r="K2" t="n">
-        <v>59.63617891758449</v>
+        <v>59.63617891758437</v>
       </c>
       <c r="L2" t="n">
-        <v>60.50697542332628</v>
+        <v>60.50697542332637</v>
       </c>
       <c r="M2" t="n">
-        <v>60.59475765152727</v>
+        <v>60.59475765152732</v>
       </c>
       <c r="N2" t="n">
-        <v>60.50328750188022</v>
+        <v>60.50328750188024</v>
       </c>
       <c r="O2" t="n">
         <v>60.43413616770317</v>
       </c>
       <c r="P2" t="n">
-        <v>60.39223064728419</v>
+        <v>60.3922306472842</v>
       </c>
       <c r="Q2" t="n">
-        <v>60.37143458903724</v>
+        <v>60.37143458903723</v>
       </c>
       <c r="R2" t="n">
-        <v>60.37480798424234</v>
+        <v>60.37480798424235</v>
       </c>
       <c r="S2" t="n">
-        <v>60.4126891999448</v>
+        <v>60.41268919994481</v>
       </c>
       <c r="T2" t="n">
-        <v>60.5074284030237</v>
+        <v>60.50742840302368</v>
       </c>
       <c r="U2" t="n">
-        <v>60.67074266145185</v>
+        <v>60.67074266145184</v>
       </c>
       <c r="V2" t="n">
         <v>60.89120553189798</v>
       </c>
       <c r="W2" t="n">
-        <v>61.14591940195381</v>
+        <v>61.14591940195383</v>
       </c>
       <c r="X2" t="n">
-        <v>61.41724511998399</v>
+        <v>61.417245119984</v>
       </c>
       <c r="Y2" t="n">
         <v>61.70001104877031</v>
@@ -626,177 +614,177 @@
         <v>62.81015339720234</v>
       </c>
       <c r="AD2" t="n">
-        <v>63.07660008668255</v>
+        <v>63.07660008668254</v>
       </c>
       <c r="AE2" t="n">
-        <v>63.34331430478771</v>
+        <v>63.34331430478777</v>
       </c>
       <c r="AF2" t="n">
-        <v>63.60922681231569</v>
+        <v>63.60922681231576</v>
       </c>
       <c r="AG2" t="n">
-        <v>63.87392460174893</v>
+        <v>63.87392460174905</v>
       </c>
       <c r="AH2" t="n">
-        <v>64.13717435853498</v>
+        <v>64.13717435853496</v>
       </c>
       <c r="AI2" t="n">
-        <v>64.3996832023021</v>
+        <v>64.39968320230199</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>10.0.2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.23008201664231</v>
+        <v>34.27076504450867</v>
       </c>
       <c r="C3" t="n">
-        <v>40.99100799093712</v>
+        <v>36.5619119895123</v>
       </c>
       <c r="D3" t="n">
-        <v>42.72849407553282</v>
+        <v>39.30898834499447</v>
       </c>
       <c r="E3" t="n">
-        <v>44.44302237354142</v>
+        <v>42.50296577770432</v>
       </c>
       <c r="F3" t="n">
-        <v>46.139933153115</v>
+        <v>46.13993315311463</v>
       </c>
       <c r="G3" t="n">
-        <v>47.83296020737234</v>
+        <v>47.83296020737197</v>
       </c>
       <c r="H3" t="n">
-        <v>49.55727264681589</v>
+        <v>49.55727264681552</v>
       </c>
       <c r="I3" t="n">
-        <v>51.35391249428419</v>
+        <v>51.35391249428395</v>
       </c>
       <c r="J3" t="n">
-        <v>52.67214500719867</v>
+        <v>52.67214500719863</v>
       </c>
       <c r="K3" t="n">
-        <v>53.68659683268116</v>
+        <v>53.6865968326812</v>
       </c>
       <c r="L3" t="n">
-        <v>54.5351534976713</v>
+        <v>54.53515349767136</v>
       </c>
       <c r="M3" t="n">
-        <v>55.29888378433965</v>
+        <v>55.29888378433972</v>
       </c>
       <c r="N3" t="n">
-        <v>55.99688217782916</v>
+        <v>55.99688217782919</v>
       </c>
       <c r="O3" t="n">
-        <v>56.62611828929185</v>
+        <v>56.62611828929189</v>
       </c>
       <c r="P3" t="n">
-        <v>57.17532861118059</v>
+        <v>57.17532861118061</v>
       </c>
       <c r="Q3" t="n">
         <v>57.63545227269096</v>
       </c>
       <c r="R3" t="n">
-        <v>58.02337126022063</v>
+        <v>58.02337126022065</v>
       </c>
       <c r="S3" t="n">
-        <v>58.36730800687394</v>
+        <v>58.36730800687395</v>
       </c>
       <c r="T3" t="n">
-        <v>58.68938184013569</v>
+        <v>58.68938184013568</v>
       </c>
       <c r="U3" t="n">
         <v>58.99262357217851</v>
       </c>
       <c r="V3" t="n">
-        <v>59.276186629942</v>
+        <v>59.27618662994201</v>
       </c>
       <c r="W3" t="n">
-        <v>59.54153093159555</v>
+        <v>59.54153093159554</v>
       </c>
       <c r="X3" t="n">
-        <v>59.78983960949884</v>
+        <v>59.78983960949885</v>
       </c>
       <c r="Y3" t="n">
-        <v>60.02692066910433</v>
+        <v>60.02692066910432</v>
       </c>
       <c r="Z3" t="n">
-        <v>60.26164956707193</v>
+        <v>60.26164956707195</v>
       </c>
       <c r="AA3" t="n">
         <v>60.4973112912061</v>
       </c>
       <c r="AB3" t="n">
-        <v>60.73454134225792</v>
+        <v>60.7345413422579</v>
       </c>
       <c r="AC3" t="n">
-        <v>60.9889166172828</v>
+        <v>60.98891661728281</v>
       </c>
       <c r="AD3" t="n">
-        <v>61.24620780054686</v>
+        <v>61.24620780054685</v>
       </c>
       <c r="AE3" t="n">
         <v>61.5061609054171</v>
       </c>
       <c r="AF3" t="n">
-        <v>61.76870486364096</v>
+        <v>61.76870486364101</v>
       </c>
       <c r="AG3" t="n">
-        <v>62.03351973894407</v>
+        <v>62.03351973894397</v>
       </c>
       <c r="AH3" t="n">
-        <v>62.30020468920053</v>
+        <v>62.30020468920046</v>
       </c>
       <c r="AI3" t="n">
-        <v>62.56844968193275</v>
+        <v>62.56844968193292</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>10.0.3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.41574244555444</v>
+        <v>31.02108581046121</v>
       </c>
       <c r="C4" t="n">
-        <v>34.11352579790022</v>
+        <v>32.33240999904111</v>
       </c>
       <c r="D4" t="n">
-        <v>35.79682188928575</v>
+        <v>34.12351103505463</v>
       </c>
       <c r="E4" t="n">
-        <v>37.46279123846815</v>
+        <v>36.38568641959574</v>
       </c>
       <c r="F4" t="n">
-        <v>39.11081288035879</v>
+        <v>39.1108128803588</v>
       </c>
       <c r="G4" t="n">
         <v>40.74725538007534</v>
       </c>
       <c r="H4" t="n">
-        <v>42.39024545896417</v>
+        <v>42.39024545896416</v>
       </c>
       <c r="I4" t="n">
         <v>44.07662730655635</v>
       </c>
       <c r="J4" t="n">
-        <v>45.57127789421411</v>
+        <v>45.57127789421412</v>
       </c>
       <c r="K4" t="n">
-        <v>46.96389067911053</v>
+        <v>46.96389067911054</v>
       </c>
       <c r="L4" t="n">
-        <v>48.27950360922272</v>
+        <v>48.27950360922271</v>
       </c>
       <c r="M4" t="n">
-        <v>49.41398745921118</v>
+        <v>49.41398745921121</v>
       </c>
       <c r="N4" t="n">
-        <v>50.25236272216551</v>
+        <v>50.25236272216554</v>
       </c>
       <c r="O4" t="n">
         <v>50.90269342472541</v>
@@ -805,31 +793,31 @@
         <v>51.48946235890529</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.0434851738676</v>
+        <v>52.04348517386761</v>
       </c>
       <c r="R4" t="n">
-        <v>52.56358464119306</v>
+        <v>52.56358464119307</v>
       </c>
       <c r="S4" t="n">
-        <v>53.04010602410492</v>
+        <v>53.04010602410489</v>
       </c>
       <c r="T4" t="n">
-        <v>53.4684291126408</v>
+        <v>53.46842911264081</v>
       </c>
       <c r="U4" t="n">
-        <v>53.86402069867095</v>
+        <v>53.86402069867093</v>
       </c>
       <c r="V4" t="n">
         <v>54.24993167485339</v>
       </c>
       <c r="W4" t="n">
-        <v>54.63994896907883</v>
+        <v>54.63994896907882</v>
       </c>
       <c r="X4" t="n">
-        <v>55.02339863205486</v>
+        <v>55.02339863205487</v>
       </c>
       <c r="Y4" t="n">
-        <v>55.38604477250286</v>
+        <v>55.38604477250287</v>
       </c>
       <c r="Z4" t="n">
         <v>55.73070854597778</v>
@@ -841,56 +829,56 @@
         <v>56.3581535301806</v>
       </c>
       <c r="AC4" t="n">
-        <v>56.59193939793339</v>
+        <v>56.59193939793338</v>
       </c>
       <c r="AD4" t="n">
-        <v>56.81595611876591</v>
+        <v>56.8159561187659</v>
       </c>
       <c r="AE4" t="n">
-        <v>57.03727034245817</v>
+        <v>57.03727034245819</v>
       </c>
       <c r="AF4" t="n">
-        <v>57.25525079006221</v>
+        <v>57.25525079006211</v>
       </c>
       <c r="AG4" t="n">
-        <v>57.46886986129894</v>
+        <v>57.46886986129901</v>
       </c>
       <c r="AH4" t="n">
-        <v>57.67596016690009</v>
+        <v>57.6759601669001</v>
       </c>
       <c r="AI4" t="n">
-        <v>57.87444916363336</v>
+        <v>57.87444916363348</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>10.0.1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.65399028487588</v>
+        <v>22.65399028487575</v>
       </c>
       <c r="C5" t="n">
         <v>24.19249770547814</v>
       </c>
       <c r="D5" t="n">
-        <v>25.69586102954656</v>
+        <v>25.69586102954658</v>
       </c>
       <c r="E5" t="n">
-        <v>27.15542802002695</v>
+        <v>27.15542802002686</v>
       </c>
       <c r="F5" t="n">
-        <v>28.55974903207631</v>
+        <v>28.55974903207634</v>
       </c>
       <c r="G5" t="n">
-        <v>29.89662975199906</v>
+        <v>29.89662975199908</v>
       </c>
       <c r="H5" t="n">
-        <v>31.16663647021999</v>
+        <v>31.16663647021998</v>
       </c>
       <c r="I5" t="n">
-        <v>32.38836911452447</v>
+        <v>32.38836911452448</v>
       </c>
       <c r="J5" t="n">
         <v>33.45422515631378</v>
@@ -899,7 +887,7 @@
         <v>34.29575629820062</v>
       </c>
       <c r="L5" t="n">
-        <v>34.94657509069954</v>
+        <v>34.94657509069953</v>
       </c>
       <c r="M5" t="n">
         <v>35.41674216630228</v>
@@ -908,7 +896,7 @@
         <v>35.70028712976484</v>
       </c>
       <c r="O5" t="n">
-        <v>35.80105521897073</v>
+        <v>35.80105521897072</v>
       </c>
       <c r="P5" t="n">
         <v>35.76095795816342</v>
@@ -920,59 +908,59 @@
         <v>35.4091775039415</v>
       </c>
       <c r="S5" t="n">
-        <v>35.15058717257534</v>
+        <v>35.15058717257532</v>
       </c>
       <c r="T5" t="n">
-        <v>34.86887945034633</v>
+        <v>34.86887945034632</v>
       </c>
       <c r="U5" t="n">
-        <v>34.57587428982187</v>
+        <v>34.57587428982186</v>
       </c>
       <c r="V5" t="n">
         <v>34.27732216915931</v>
       </c>
       <c r="W5" t="n">
-        <v>33.98736322893907</v>
+        <v>33.98736322893908</v>
       </c>
       <c r="X5" t="n">
-        <v>33.7530673365023</v>
+        <v>33.75306733650226</v>
       </c>
       <c r="Y5" t="n">
-        <v>33.80390089524575</v>
+        <v>33.80390089524573</v>
       </c>
       <c r="Z5" t="n">
-        <v>34.53930692082074</v>
+        <v>34.53930692082071</v>
       </c>
       <c r="AA5" t="n">
-        <v>35.67692664030059</v>
+        <v>35.67692664030057</v>
       </c>
       <c r="AB5" t="n">
-        <v>36.6202611036072</v>
+        <v>36.62026110360716</v>
       </c>
       <c r="AC5" t="n">
         <v>37.41654780498315</v>
       </c>
       <c r="AD5" t="n">
-        <v>38.18757691881693</v>
+        <v>38.18757691881691</v>
       </c>
       <c r="AE5" t="n">
-        <v>38.9954757987924</v>
+        <v>38.99547579879234</v>
       </c>
       <c r="AF5" t="n">
-        <v>39.83920262680807</v>
+        <v>39.83920262680805</v>
       </c>
       <c r="AG5" t="n">
-        <v>40.70822781954504</v>
+        <v>40.70822781954503</v>
       </c>
       <c r="AH5" t="n">
-        <v>41.58676940521843</v>
+        <v>41.58676940521839</v>
       </c>
       <c r="AI5" t="n">
-        <v>42.45836234080253</v>
+        <v>42.45836234080254</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
@@ -981,13 +969,13 @@
         <v>12.27242543743599</v>
       </c>
       <c r="C6" t="n">
-        <v>14.07169542077592</v>
+        <v>14.07169542077591</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8509053287453</v>
+        <v>15.85090532874529</v>
       </c>
       <c r="E6" t="n">
-        <v>17.60268092030207</v>
+        <v>17.60268092030208</v>
       </c>
       <c r="F6" t="n">
         <v>19.32291799966571</v>
@@ -1023,16 +1011,16 @@
         <v>29.68920275747526</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.74116164394632</v>
+        <v>29.74116164394633</v>
       </c>
       <c r="R6" t="n">
         <v>29.75262642874656</v>
       </c>
       <c r="S6" t="n">
-        <v>29.76262728784491</v>
+        <v>29.7626272878449</v>
       </c>
       <c r="T6" t="n">
-        <v>29.78777392056912</v>
+        <v>29.78777392056911</v>
       </c>
       <c r="U6" t="n">
         <v>29.84141916174012</v>
@@ -1044,44 +1032,44 @@
         <v>30.07407096047863</v>
       </c>
       <c r="X6" t="n">
-        <v>30.28391552477293</v>
+        <v>30.28391552477294</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.58575552683945</v>
+        <v>30.58575552683944</v>
       </c>
       <c r="Z6" t="n">
-        <v>30.98773530500793</v>
+        <v>30.98773530500792</v>
       </c>
       <c r="AA6" t="n">
         <v>31.46044960849571</v>
       </c>
       <c r="AB6" t="n">
-        <v>31.99440183386822</v>
+        <v>31.99440183386823</v>
       </c>
       <c r="AC6" t="n">
-        <v>32.62329427157452</v>
+        <v>32.62329427157451</v>
       </c>
       <c r="AD6" t="n">
-        <v>33.26186098901955</v>
+        <v>33.26186098901954</v>
       </c>
       <c r="AE6" t="n">
         <v>33.90728735564456</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.56185751374279</v>
+        <v>34.56185751374274</v>
       </c>
       <c r="AG6" t="n">
-        <v>35.22740834779857</v>
+        <v>35.22740834779864</v>
       </c>
       <c r="AH6" t="n">
-        <v>35.90440261141272</v>
+        <v>35.90440261141283</v>
       </c>
       <c r="AI6" t="n">
-        <v>36.59539978770995</v>
+        <v>36.59539978770979</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>5.0.1</t>
         </is>
@@ -1093,7 +1081,7 @@
         <v>14.62171642063212</v>
       </c>
       <c r="D7" t="n">
-        <v>13.99553192260297</v>
+        <v>13.99553192260295</v>
       </c>
       <c r="E7" t="n">
         <v>13.41389705056306</v>
@@ -1123,140 +1111,140 @@
         <v>15.7016525746499</v>
       </c>
       <c r="N7" t="n">
-        <v>17.72399427439658</v>
+        <v>17.72399427439659</v>
       </c>
       <c r="O7" t="n">
         <v>20.17957997978379</v>
       </c>
       <c r="P7" t="n">
-        <v>23.10653805429703</v>
+        <v>23.10653805429705</v>
       </c>
       <c r="Q7" t="n">
         <v>26.19577098768931</v>
       </c>
       <c r="R7" t="n">
-        <v>28.97924382597849</v>
+        <v>28.97924382597846</v>
       </c>
       <c r="S7" t="n">
         <v>31.46242058819539</v>
       </c>
       <c r="T7" t="n">
-        <v>33.76688057053057</v>
+        <v>33.76688057053056</v>
       </c>
       <c r="U7" t="n">
         <v>35.91493010096741</v>
       </c>
       <c r="V7" t="n">
-        <v>37.91614513908536</v>
+        <v>37.91614513908537</v>
       </c>
       <c r="W7" t="n">
-        <v>39.74221257818997</v>
+        <v>39.74221257818995</v>
       </c>
       <c r="X7" t="n">
-        <v>41.15738729718613</v>
+        <v>41.15738729718609</v>
       </c>
       <c r="Y7" t="n">
-        <v>41.7800218957066</v>
+        <v>41.78002189570655</v>
       </c>
       <c r="Z7" t="n">
-        <v>41.88175896522064</v>
+        <v>41.88175896522063</v>
       </c>
       <c r="AA7" t="n">
-        <v>41.97872967143431</v>
+        <v>41.97872967143429</v>
       </c>
       <c r="AB7" t="n">
-        <v>42.17622940677678</v>
+        <v>42.17622940677679</v>
       </c>
       <c r="AC7" t="n">
         <v>42.5358540281745</v>
       </c>
       <c r="AD7" t="n">
-        <v>42.89306401917201</v>
+        <v>42.89306401917202</v>
       </c>
       <c r="AE7" t="n">
         <v>43.26204718694049</v>
       </c>
       <c r="AF7" t="n">
-        <v>43.64898322518423</v>
+        <v>43.6489832251842</v>
       </c>
       <c r="AG7" t="n">
-        <v>44.05331740911731</v>
+        <v>44.05331740911724</v>
       </c>
       <c r="AH7" t="n">
-        <v>44.47222679062247</v>
+        <v>44.47222679062232</v>
       </c>
       <c r="AI7" t="n">
-        <v>44.90179041002417</v>
+        <v>44.90179041002424</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2.5.1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.19404106573069</v>
+        <v>33.68827100516449</v>
       </c>
       <c r="C8" t="n">
-        <v>39.66614475580822</v>
+        <v>35.67970278299735</v>
       </c>
       <c r="D8" t="n">
-        <v>41.11087624675267</v>
+        <v>38.0560310770934</v>
       </c>
       <c r="E8" t="n">
-        <v>42.53014557884531</v>
+        <v>40.80761470699574</v>
       </c>
       <c r="F8" t="n">
-        <v>43.92964547617654</v>
+        <v>43.92964547617657</v>
       </c>
       <c r="G8" t="n">
-        <v>45.31764663921674</v>
+        <v>45.31764663921675</v>
       </c>
       <c r="H8" t="n">
-        <v>46.7070447402231</v>
+        <v>46.70704474022311</v>
       </c>
       <c r="I8" t="n">
         <v>48.11931546749222</v>
       </c>
       <c r="J8" t="n">
-        <v>49.30328865091165</v>
+        <v>49.30328865091167</v>
       </c>
       <c r="K8" t="n">
         <v>50.36472618079488</v>
       </c>
       <c r="L8" t="n">
-        <v>51.25447452824367</v>
+        <v>51.25447452824366</v>
       </c>
       <c r="M8" t="n">
-        <v>51.99728671704432</v>
+        <v>51.99728671704433</v>
       </c>
       <c r="N8" t="n">
-        <v>52.65525156761162</v>
+        <v>52.65525156761163</v>
       </c>
       <c r="O8" t="n">
         <v>53.25074448759619</v>
       </c>
       <c r="P8" t="n">
-        <v>53.7915602347606</v>
+        <v>53.79156023476061</v>
       </c>
       <c r="Q8" t="n">
         <v>54.27811939319047</v>
       </c>
       <c r="R8" t="n">
-        <v>54.69676633453149</v>
+        <v>54.69676633453147</v>
       </c>
       <c r="S8" t="n">
         <v>55.03892671519743</v>
       </c>
       <c r="T8" t="n">
-        <v>55.29502208908349</v>
+        <v>55.29502208908348</v>
       </c>
       <c r="U8" t="n">
         <v>55.45064439914165</v>
       </c>
       <c r="V8" t="n">
-        <v>55.50970155636181</v>
+        <v>55.5097015563618</v>
       </c>
       <c r="W8" t="n">
         <v>55.50193823763501</v>
@@ -1268,16 +1256,16 @@
         <v>55.40616075616497</v>
       </c>
       <c r="Z8" t="n">
-        <v>55.34970753231066</v>
+        <v>55.34970753231067</v>
       </c>
       <c r="AA8" t="n">
         <v>55.30330398040707</v>
       </c>
       <c r="AB8" t="n">
-        <v>55.2730170703317</v>
+        <v>55.27301707033169</v>
       </c>
       <c r="AC8" t="n">
-        <v>55.30872837704317</v>
+        <v>55.30872837704316</v>
       </c>
       <c r="AD8" t="n">
         <v>55.34208566751252</v>
@@ -1286,59 +1274,59 @@
         <v>55.38025776976863</v>
       </c>
       <c r="AF8" t="n">
-        <v>55.42615923295034</v>
+        <v>55.42615923295032</v>
       </c>
       <c r="AG8" t="n">
-        <v>55.48076716310037</v>
+        <v>55.48076716310036</v>
       </c>
       <c r="AH8" t="n">
-        <v>55.54405117797021</v>
+        <v>55.5440511779701</v>
       </c>
       <c r="AI8" t="n">
-        <v>55.61439114834478</v>
+        <v>55.61439114834481</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.5905281190532</v>
+        <v>36.26061198355985</v>
       </c>
       <c r="C9" t="n">
-        <v>44.15042142368506</v>
+        <v>38.42650465925377</v>
       </c>
       <c r="D9" t="n">
-        <v>44.70347530888805</v>
+        <v>40.73838874380611</v>
       </c>
       <c r="E9" t="n">
-        <v>45.24795298134924</v>
+        <v>43.19199504483359</v>
       </c>
       <c r="F9" t="n">
-        <v>45.78150881829043</v>
+        <v>45.78150881829047</v>
       </c>
       <c r="G9" t="n">
-        <v>46.30092106784213</v>
+        <v>46.30092106784222</v>
       </c>
       <c r="H9" t="n">
-        <v>46.80213063535321</v>
+        <v>46.80213063535329</v>
       </c>
       <c r="I9" t="n">
         <v>47.28293163593818</v>
       </c>
       <c r="J9" t="n">
-        <v>47.74676719691372</v>
+        <v>47.74676719691374</v>
       </c>
       <c r="K9" t="n">
-        <v>48.14528111721706</v>
+        <v>48.14528111721705</v>
       </c>
       <c r="L9" t="n">
-        <v>48.50478924848344</v>
+        <v>48.50478924848342</v>
       </c>
       <c r="M9" t="n">
-        <v>48.84503725845583</v>
+        <v>48.84503725845582</v>
       </c>
       <c r="N9" t="n">
         <v>49.17492940443269</v>
@@ -1350,19 +1338,19 @@
         <v>49.78960030359693</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.06843889287128</v>
+        <v>50.06843889287126</v>
       </c>
       <c r="R9" t="n">
         <v>50.33036985877619</v>
       </c>
       <c r="S9" t="n">
-        <v>50.5739068204461</v>
+        <v>50.57390682044611</v>
       </c>
       <c r="T9" t="n">
-        <v>50.79498667320001</v>
+        <v>50.79498667319999</v>
       </c>
       <c r="U9" t="n">
-        <v>50.99004171894686</v>
+        <v>50.99004171894687</v>
       </c>
       <c r="V9" t="n">
         <v>51.15668395491195</v>
@@ -1377,107 +1365,107 @@
         <v>51.48589587466947</v>
       </c>
       <c r="Z9" t="n">
-        <v>51.5408911234954</v>
+        <v>51.54089112349541</v>
       </c>
       <c r="AA9" t="n">
-        <v>51.55150233973188</v>
+        <v>51.5515023397319</v>
       </c>
       <c r="AB9" t="n">
-        <v>51.52226827613023</v>
+        <v>51.52226827613024</v>
       </c>
       <c r="AC9" t="n">
-        <v>51.44425694420443</v>
+        <v>51.4442569442044</v>
       </c>
       <c r="AD9" t="n">
-        <v>51.37068661318236</v>
+        <v>51.37068661318233</v>
       </c>
       <c r="AE9" t="n">
-        <v>51.29963277861349</v>
+        <v>51.29963277861352</v>
       </c>
       <c r="AF9" t="n">
-        <v>51.22633344319058</v>
+        <v>51.22633344319055</v>
       </c>
       <c r="AG9" t="n">
-        <v>51.14545115632441</v>
+        <v>51.14545115632436</v>
       </c>
       <c r="AH9" t="n">
-        <v>51.05320956010484</v>
+        <v>51.05320956010487</v>
       </c>
       <c r="AI9" t="n">
-        <v>50.95067889404198</v>
+        <v>50.95067889404196</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2.5.3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.6824276358586</v>
+        <v>11.68242763585753</v>
       </c>
       <c r="C10" t="n">
-        <v>14.23286595948776</v>
+        <v>14.23286595948683</v>
       </c>
       <c r="D10" t="n">
-        <v>16.80115669228747</v>
+        <v>16.80115669228669</v>
       </c>
       <c r="E10" t="n">
-        <v>19.38866396905577</v>
+        <v>19.38866396905518</v>
       </c>
       <c r="F10" t="n">
-        <v>21.99148216602064</v>
+        <v>21.99148216602024</v>
       </c>
       <c r="G10" t="n">
-        <v>24.59992836049929</v>
+        <v>24.59992836049903</v>
       </c>
       <c r="H10" t="n">
-        <v>27.20959577522122</v>
+        <v>27.2095957752211</v>
       </c>
       <c r="I10" t="n">
         <v>29.83819429081204</v>
       </c>
       <c r="J10" t="n">
-        <v>31.86835812496091</v>
+        <v>31.86835812496088</v>
       </c>
       <c r="K10" t="n">
-        <v>33.54689916377068</v>
+        <v>33.54689916377063</v>
       </c>
       <c r="L10" t="n">
-        <v>35.27643234711767</v>
+        <v>35.2764323471176</v>
       </c>
       <c r="M10" t="n">
-        <v>37.05023564548194</v>
+        <v>37.05023564548187</v>
       </c>
       <c r="N10" t="n">
-        <v>38.78902881703291</v>
+        <v>38.78902881703284</v>
       </c>
       <c r="O10" t="n">
-        <v>40.55669201953833</v>
+        <v>40.55669201953829</v>
       </c>
       <c r="P10" t="n">
-        <v>42.51606939068305</v>
+        <v>42.51606939068303</v>
       </c>
       <c r="Q10" t="n">
-        <v>44.09018625109334</v>
+        <v>44.09018625109339</v>
       </c>
       <c r="R10" t="n">
         <v>44.62363336488429</v>
       </c>
       <c r="S10" t="n">
-        <v>44.8706869946046</v>
+        <v>44.87068699460461</v>
       </c>
       <c r="T10" t="n">
-        <v>45.08244786937117</v>
+        <v>45.0824478693712</v>
       </c>
       <c r="U10" t="n">
-        <v>45.27968242300443</v>
+        <v>45.27968242300442</v>
       </c>
       <c r="V10" t="n">
-        <v>45.46242406330916</v>
+        <v>45.46242406330919</v>
       </c>
       <c r="W10" t="n">
-        <v>45.6252448754093</v>
+        <v>45.62524487540932</v>
       </c>
       <c r="X10" t="n">
         <v>45.75262602853154</v>
@@ -1486,74 +1474,74 @@
         <v>45.83555606204462</v>
       </c>
       <c r="Z10" t="n">
-        <v>45.87843217329932</v>
+        <v>45.8784321732993</v>
       </c>
       <c r="AA10" t="n">
         <v>45.88657819714186</v>
       </c>
       <c r="AB10" t="n">
-        <v>45.85826684561349</v>
+        <v>45.85826684561351</v>
       </c>
       <c r="AC10" t="n">
-        <v>45.73069275978859</v>
+        <v>45.73069275978858</v>
       </c>
       <c r="AD10" t="n">
         <v>45.59394335546225</v>
       </c>
       <c r="AE10" t="n">
-        <v>45.45039732601604</v>
+        <v>45.45039732601601</v>
       </c>
       <c r="AF10" t="n">
-        <v>45.29897745491217</v>
+        <v>45.29897745491218</v>
       </c>
       <c r="AG10" t="n">
-        <v>45.13910206378664</v>
+        <v>45.13910206378667</v>
       </c>
       <c r="AH10" t="n">
-        <v>44.97024024423733</v>
+        <v>44.97024024423742</v>
       </c>
       <c r="AI10" t="n">
-        <v>44.79219124271129</v>
+        <v>44.79219124271139</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1.25.2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.368059047319509</v>
+        <v>9.368059047319511</v>
       </c>
       <c r="C11" t="n">
         <v>10.90648062422888</v>
       </c>
       <c r="D11" t="n">
-        <v>12.43111257550109</v>
+        <v>12.43111257550107</v>
       </c>
       <c r="E11" t="n">
-        <v>13.93813532956152</v>
+        <v>13.93813532956151</v>
       </c>
       <c r="F11" t="n">
-        <v>15.42412500758638</v>
+        <v>15.42412500758637</v>
       </c>
       <c r="G11" t="n">
-        <v>16.88773715190946</v>
+        <v>16.88773715190947</v>
       </c>
       <c r="H11" t="n">
         <v>18.33156921238818</v>
       </c>
       <c r="I11" t="n">
-        <v>19.76002249160449</v>
+        <v>19.76002249160448</v>
       </c>
       <c r="J11" t="n">
         <v>20.95276522206068</v>
       </c>
       <c r="K11" t="n">
-        <v>22.00785734617495</v>
+        <v>22.00785734617494</v>
       </c>
       <c r="L11" t="n">
-        <v>22.95869244341818</v>
+        <v>22.95869244341817</v>
       </c>
       <c r="M11" t="n">
         <v>23.82108401836467</v>
@@ -1568,22 +1556,22 @@
         <v>25.53845387285821</v>
       </c>
       <c r="Q11" t="n">
-        <v>25.82816542200582</v>
+        <v>25.82816542200583</v>
       </c>
       <c r="R11" t="n">
-        <v>26.00040899203248</v>
+        <v>26.00040899203247</v>
       </c>
       <c r="S11" t="n">
         <v>26.08312347890518</v>
       </c>
       <c r="T11" t="n">
-        <v>26.09569144393383</v>
+        <v>26.09569144393382</v>
       </c>
       <c r="U11" t="n">
         <v>26.04429647752721</v>
       </c>
       <c r="V11" t="n">
-        <v>25.93335279348132</v>
+        <v>25.93335279348134</v>
       </c>
       <c r="W11" t="n">
         <v>25.77609167714032</v>
@@ -1595,13 +1583,13 @@
         <v>25.35186104094457</v>
       </c>
       <c r="Z11" t="n">
-        <v>25.06441576283486</v>
+        <v>25.06441576283487</v>
       </c>
       <c r="AA11" t="n">
         <v>24.72446349160832</v>
       </c>
       <c r="AB11" t="n">
-        <v>24.33867233875435</v>
+        <v>24.33867233875434</v>
       </c>
       <c r="AC11" t="n">
         <v>23.89411944544868</v>
@@ -1616,35 +1604,35 @@
         <v>22.5717010131331</v>
       </c>
       <c r="AG11" t="n">
-        <v>22.12332831888235</v>
+        <v>22.12332831888236</v>
       </c>
       <c r="AH11" t="n">
         <v>21.66900623155163</v>
       </c>
       <c r="AI11" t="n">
-        <v>21.2088744609392</v>
+        <v>21.20887446093919</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1.25.1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.41579629953799</v>
+        <v>5.415796299537988</v>
       </c>
       <c r="C12" t="n">
-        <v>6.495672457368168</v>
+        <v>6.495672457368165</v>
       </c>
       <c r="D12" t="n">
-        <v>7.607999055328222</v>
+        <v>7.607999055328232</v>
       </c>
       <c r="E12" t="n">
-        <v>8.749974542119768</v>
+        <v>8.749974542119766</v>
       </c>
       <c r="F12" t="n">
-        <v>9.918662473520204</v>
+        <v>9.918662473520202</v>
       </c>
       <c r="G12" t="n">
         <v>11.11292425780555</v>
@@ -1656,13 +1644,13 @@
         <v>13.61567840054283</v>
       </c>
       <c r="J12" t="n">
-        <v>15.19912377813327</v>
+        <v>15.19912377813328</v>
       </c>
       <c r="K12" t="n">
         <v>16.87700120720123</v>
       </c>
       <c r="L12" t="n">
-        <v>18.54715569794759</v>
+        <v>18.54715569794758</v>
       </c>
       <c r="M12" t="n">
         <v>20.1435796000374</v>
@@ -1680,13 +1668,13 @@
         <v>25.42034029409602</v>
       </c>
       <c r="R12" t="n">
-        <v>26.33864231584927</v>
+        <v>26.33864231584926</v>
       </c>
       <c r="S12" t="n">
         <v>27.01403436169558</v>
       </c>
       <c r="T12" t="n">
-        <v>27.37716955681429</v>
+        <v>27.3771695568143</v>
       </c>
       <c r="U12" t="n">
         <v>27.45306076839028</v>
@@ -1704,7 +1692,7 @@
         <v>26.57585380946519</v>
       </c>
       <c r="Z12" t="n">
-        <v>26.23645371920704</v>
+        <v>26.23645371920703</v>
       </c>
       <c r="AA12" t="n">
         <v>25.85865501233828</v>
@@ -1719,65 +1707,65 @@
         <v>24.63925045290905</v>
       </c>
       <c r="AE12" t="n">
-        <v>24.24692176311375</v>
+        <v>24.24692176311374</v>
       </c>
       <c r="AF12" t="n">
-        <v>23.859527047725</v>
+        <v>23.85952704772501</v>
       </c>
       <c r="AG12" t="n">
-        <v>23.47505408167905</v>
+        <v>23.47505408167904</v>
       </c>
       <c r="AH12" t="n">
-        <v>23.09223587254758</v>
+        <v>23.09223587254761</v>
       </c>
       <c r="AI12" t="n">
-        <v>22.71077085076044</v>
+        <v>22.71077085076033</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.481983953343595</v>
+        <v>5.48198395334359</v>
       </c>
       <c r="C13" t="n">
-        <v>5.278763834102037</v>
+        <v>5.278763834102035</v>
       </c>
       <c r="D13" t="n">
-        <v>5.099375272778544</v>
+        <v>5.099375272778543</v>
       </c>
       <c r="E13" t="n">
-        <v>4.936870888561362</v>
+        <v>4.936870888561357</v>
       </c>
       <c r="F13" t="n">
-        <v>4.787238928954862</v>
+        <v>4.787238928954859</v>
       </c>
       <c r="G13" t="n">
-        <v>4.651596554627714</v>
+        <v>4.651596554627711</v>
       </c>
       <c r="H13" t="n">
-        <v>4.539563247765598</v>
+        <v>4.539563247765596</v>
       </c>
       <c r="I13" t="n">
-        <v>4.492857981684183</v>
+        <v>4.492857981684182</v>
       </c>
       <c r="J13" t="n">
         <v>4.799858417827022</v>
       </c>
       <c r="K13" t="n">
-        <v>5.324724254071972</v>
+        <v>5.324724254071973</v>
       </c>
       <c r="L13" t="n">
         <v>6.11358052355058</v>
       </c>
       <c r="M13" t="n">
-        <v>7.25206569582882</v>
+        <v>7.252065695828822</v>
       </c>
       <c r="N13" t="n">
-        <v>8.794934111947883</v>
+        <v>8.79493411194788</v>
       </c>
       <c r="O13" t="n">
         <v>10.73672918190889</v>
@@ -1786,83 +1774,83 @@
         <v>13.05216520189678</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.71791478566731</v>
+        <v>15.7179147856673</v>
       </c>
       <c r="R13" t="n">
-        <v>18.69214140979287</v>
+        <v>18.69214140979286</v>
       </c>
       <c r="S13" t="n">
-        <v>21.90895631698192</v>
+        <v>21.90895631698189</v>
       </c>
       <c r="T13" t="n">
-        <v>25.23091793463893</v>
+        <v>25.23091793463896</v>
       </c>
       <c r="U13" t="n">
-        <v>28.33118139737419</v>
+        <v>28.33118139737418</v>
       </c>
       <c r="V13" t="n">
-        <v>30.38880335799582</v>
+        <v>30.38880335799587</v>
       </c>
       <c r="W13" t="n">
-        <v>30.69881320252514</v>
+        <v>30.69881320252508</v>
       </c>
       <c r="X13" t="n">
-        <v>30.20529808480313</v>
+        <v>30.20529808480302</v>
       </c>
       <c r="Y13" t="n">
-        <v>29.6520878735847</v>
+        <v>29.65208787358458</v>
       </c>
       <c r="Z13" t="n">
-        <v>29.04733808696346</v>
+        <v>29.04733808696337</v>
       </c>
       <c r="AA13" t="n">
-        <v>28.21047454467879</v>
+        <v>28.21047454467871</v>
       </c>
       <c r="AB13" t="n">
-        <v>26.86398778032107</v>
+        <v>26.86398778032101</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.95911284138998</v>
+        <v>23.95911284138999</v>
       </c>
       <c r="AD13" t="n">
         <v>20.92081269166572</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.78251615736961</v>
+        <v>17.78251615736955</v>
       </c>
       <c r="AF13" t="n">
-        <v>14.56454960413662</v>
+        <v>14.5645496041366</v>
       </c>
       <c r="AG13" t="n">
         <v>11.28644494828352</v>
       </c>
       <c r="AH13" t="n">
-        <v>7.96709849762723</v>
+        <v>7.967098497627246</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.623423726326084</v>
+        <v>4.623423726326096</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.625.1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.0962150967113</v>
+        <v>10.09621509671131</v>
       </c>
       <c r="C14" t="n">
         <v>11.06779055195303</v>
       </c>
       <c r="D14" t="n">
-        <v>12.05469599192569</v>
+        <v>12.05469599192568</v>
       </c>
       <c r="E14" t="n">
-        <v>13.05364975670344</v>
+        <v>13.05364975670343</v>
       </c>
       <c r="F14" t="n">
-        <v>14.05965127207935</v>
+        <v>14.05965127207934</v>
       </c>
       <c r="G14" t="n">
         <v>15.06554853347135</v>
@@ -1874,25 +1862,25 @@
         <v>17.06788622385001</v>
       </c>
       <c r="J14" t="n">
-        <v>18.12434840802388</v>
+        <v>18.12434840802389</v>
       </c>
       <c r="K14" t="n">
         <v>19.21250755953971</v>
       </c>
       <c r="L14" t="n">
-        <v>20.30024723426029</v>
+        <v>20.30024723426028</v>
       </c>
       <c r="M14" t="n">
-        <v>21.33718666394913</v>
+        <v>21.33718666394912</v>
       </c>
       <c r="N14" t="n">
         <v>22.2875792877688</v>
       </c>
       <c r="O14" t="n">
-        <v>23.14888448158467</v>
+        <v>23.14888448158468</v>
       </c>
       <c r="P14" t="n">
-        <v>23.90668109315153</v>
+        <v>23.90668109315154</v>
       </c>
       <c r="Q14" t="n">
         <v>24.53958595411213</v>
@@ -1910,19 +1898,19 @@
         <v>25.25214664297702</v>
       </c>
       <c r="V14" t="n">
-        <v>24.97645830757514</v>
+        <v>24.97645830757515</v>
       </c>
       <c r="W14" t="n">
         <v>24.58066252618072</v>
       </c>
       <c r="X14" t="n">
-        <v>24.11659699753055</v>
+        <v>24.11659699753056</v>
       </c>
       <c r="Y14" t="n">
         <v>23.62624649672864</v>
       </c>
       <c r="Z14" t="n">
-        <v>23.12182362311609</v>
+        <v>23.12182362311608</v>
       </c>
       <c r="AA14" t="n">
         <v>22.6311576389946</v>
@@ -1931,7 +1919,7 @@
         <v>22.18899558782534</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.91820326916241</v>
+        <v>21.91820326916242</v>
       </c>
       <c r="AD14" t="n">
         <v>21.6505688689328</v>
@@ -1943,17 +1931,17 @@
         <v>21.16176456499156</v>
       </c>
       <c r="AG14" t="n">
-        <v>20.94193935624551</v>
+        <v>20.9419393562455</v>
       </c>
       <c r="AH14" t="n">
-        <v>20.73524383562437</v>
+        <v>20.73524383562431</v>
       </c>
       <c r="AI14" t="n">
-        <v>20.53860360051484</v>
+        <v>20.53860360051482</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.625.2</t>
         </is>
@@ -1962,7 +1950,7 @@
         <v>14.97880472610887</v>
       </c>
       <c r="C15" t="n">
-        <v>15.57944351751272</v>
+        <v>15.57944351751273</v>
       </c>
       <c r="D15" t="n">
         <v>16.19370966324333</v>
@@ -1980,7 +1968,7 @@
         <v>19.06389264118607</v>
       </c>
       <c r="I15" t="n">
-        <v>19.93940030629773</v>
+        <v>19.93940030629774</v>
       </c>
       <c r="J15" t="n">
         <v>21.41367640041501</v>
@@ -1989,7 +1977,7 @@
         <v>23.07474646024544</v>
       </c>
       <c r="L15" t="n">
-        <v>24.90798063583745</v>
+        <v>24.90798063583744</v>
       </c>
       <c r="M15" t="n">
         <v>26.93600288758434</v>
@@ -2001,13 +1989,13 @@
         <v>31.14870049993346</v>
       </c>
       <c r="P15" t="n">
-        <v>32.84270531879156</v>
+        <v>32.84270531879155</v>
       </c>
       <c r="Q15" t="n">
         <v>33.93297339467875</v>
       </c>
       <c r="R15" t="n">
-        <v>34.29088677507529</v>
+        <v>34.29088677507527</v>
       </c>
       <c r="S15" t="n">
         <v>33.87940848705217</v>
@@ -2022,104 +2010,104 @@
         <v>28.3227833964219</v>
       </c>
       <c r="W15" t="n">
-        <v>25.56822966064899</v>
+        <v>25.56822966064898</v>
       </c>
       <c r="X15" t="n">
-        <v>22.75870214980021</v>
+        <v>22.75870214980023</v>
       </c>
       <c r="Y15" t="n">
-        <v>20.05017048388363</v>
+        <v>20.05017048388362</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.58138973719321</v>
+        <v>17.5813897371932</v>
       </c>
       <c r="AA15" t="n">
-        <v>15.45120058111228</v>
+        <v>15.45120058111227</v>
       </c>
       <c r="AB15" t="n">
         <v>13.72605558509352</v>
       </c>
       <c r="AC15" t="n">
-        <v>12.97852666348924</v>
+        <v>12.97852666348925</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.2751565991228</v>
+        <v>12.27515659912281</v>
       </c>
       <c r="AE15" t="n">
         <v>11.62918641636641</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.05211717797596</v>
+        <v>11.05211717797597</v>
       </c>
       <c r="AG15" t="n">
         <v>10.54824429278431</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.1161243831577</v>
+        <v>10.11612438315769</v>
       </c>
       <c r="AI15" t="n">
-        <v>9.749883587049682</v>
+        <v>9.749883587049681</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.625</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.875934764278943</v>
+        <v>7.875934764278981</v>
       </c>
       <c r="C16" t="n">
-        <v>8.159114249395842</v>
+        <v>8.15911424939587</v>
       </c>
       <c r="D16" t="n">
-        <v>8.444394323177217</v>
+        <v>8.444394323177244</v>
       </c>
       <c r="E16" t="n">
-        <v>8.728935076756237</v>
+        <v>8.728935076756258</v>
       </c>
       <c r="F16" t="n">
-        <v>9.011789676094482</v>
+        <v>9.011789676094496</v>
       </c>
       <c r="G16" t="n">
-        <v>9.29459790623104</v>
+        <v>9.294597906231049</v>
       </c>
       <c r="H16" t="n">
-        <v>9.583190616370644</v>
+        <v>9.583190616370645</v>
       </c>
       <c r="I16" t="n">
-        <v>9.889077187953202</v>
+        <v>9.8890771879532</v>
       </c>
       <c r="J16" t="n">
-        <v>10.23927095834338</v>
+        <v>10.23927095834337</v>
       </c>
       <c r="K16" t="n">
-        <v>10.64161661548964</v>
+        <v>10.64161661548963</v>
       </c>
       <c r="L16" t="n">
-        <v>11.07902327388063</v>
+        <v>11.07902327388062</v>
       </c>
       <c r="M16" t="n">
-        <v>11.53928324483557</v>
+        <v>11.53928324483556</v>
       </c>
       <c r="N16" t="n">
-        <v>12.01229029687076</v>
+        <v>12.01229029687075</v>
       </c>
       <c r="O16" t="n">
-        <v>12.49446773612522</v>
+        <v>12.49446773612521</v>
       </c>
       <c r="P16" t="n">
-        <v>12.98977921106769</v>
+        <v>12.98977921106768</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.50305178660629</v>
+        <v>13.50305178660628</v>
       </c>
       <c r="R16" t="n">
-        <v>14.0285791042007</v>
+        <v>14.02857910420069</v>
       </c>
       <c r="S16" t="n">
-        <v>14.53466566287803</v>
+        <v>14.53466566287802</v>
       </c>
       <c r="T16" t="n">
         <v>14.98118724301819</v>
@@ -2134,7 +2122,7 @@
         <v>15.82817968199338</v>
       </c>
       <c r="X16" t="n">
-        <v>15.9693705318173</v>
+        <v>15.96937053181731</v>
       </c>
       <c r="Y16" t="n">
         <v>16.05388730459544</v>
@@ -2158,20 +2146,20 @@
         <v>15.09211439600766</v>
       </c>
       <c r="AF16" t="n">
-        <v>14.8148024088743</v>
+        <v>14.81480240887431</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.53260855228406</v>
+        <v>14.53260855228403</v>
       </c>
       <c r="AH16" t="n">
-        <v>14.24237367254712</v>
+        <v>14.24237367254709</v>
       </c>
       <c r="AI16" t="n">
-        <v>13.94201440740004</v>
+        <v>13.94201440740007</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.313</t>
         </is>
@@ -2189,7 +2177,7 @@
         <v>13.7711930967679</v>
       </c>
       <c r="F17" t="n">
-        <v>14.23700406758374</v>
+        <v>14.23700406758375</v>
       </c>
       <c r="G17" t="n">
         <v>14.70694511763213</v>
@@ -2198,7 +2186,7 @@
         <v>15.1826039211632</v>
       </c>
       <c r="I17" t="n">
-        <v>15.67463317929404</v>
+        <v>15.67463317929405</v>
       </c>
       <c r="J17" t="n">
         <v>16.21971946412867</v>
@@ -2213,7 +2201,7 @@
         <v>17.76104596371994</v>
       </c>
       <c r="N17" t="n">
-        <v>18.18678852618909</v>
+        <v>18.1867885261891</v>
       </c>
       <c r="O17" t="n">
         <v>18.53445902146972</v>
@@ -2225,13 +2213,13 @@
         <v>18.95905847310271</v>
       </c>
       <c r="R17" t="n">
-        <v>19.01655836094872</v>
+        <v>19.01655836094873</v>
       </c>
       <c r="S17" t="n">
         <v>18.96159102693496</v>
       </c>
       <c r="T17" t="n">
-        <v>18.79055277860556</v>
+        <v>18.79055277860555</v>
       </c>
       <c r="U17" t="n">
         <v>18.50810815920168</v>
@@ -2255,7 +2243,7 @@
         <v>16.53886510867553</v>
       </c>
       <c r="AB17" t="n">
-        <v>16.30192205795085</v>
+        <v>16.30192205795084</v>
       </c>
       <c r="AC17" t="n">
         <v>16.14413098393851</v>
@@ -2264,89 +2252,89 @@
         <v>15.9950799603025</v>
       </c>
       <c r="AE17" t="n">
-        <v>15.85019924219612</v>
+        <v>15.85019924219613</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.70769981743638</v>
+        <v>15.70769981743636</v>
       </c>
       <c r="AG17" t="n">
         <v>15.56675939269608</v>
       </c>
       <c r="AH17" t="n">
-        <v>15.42709310053161</v>
+        <v>15.42709310053157</v>
       </c>
       <c r="AI17" t="n">
-        <v>15.28879288370262</v>
+        <v>15.28879288370261</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.156</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-9.251110580697528</v>
+        <v>-9.251110580697823</v>
       </c>
       <c r="C18" t="n">
-        <v>-5.966583292183509</v>
+        <v>-5.966583292183775</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.656545864632291</v>
+        <v>-2.656545864632531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.684573292560108</v>
+        <v>0.6845732925599618</v>
       </c>
       <c r="F18" t="n">
-        <v>4.062757689100859</v>
+        <v>4.062757689100762</v>
       </c>
       <c r="G18" t="n">
-        <v>7.478728281616238</v>
+        <v>7.478728281616157</v>
       </c>
       <c r="H18" t="n">
-        <v>10.91919517413459</v>
+        <v>10.91919517413456</v>
       </c>
       <c r="I18" t="n">
-        <v>14.39241868034995</v>
+        <v>14.39241868034996</v>
       </c>
       <c r="J18" t="n">
-        <v>17.43169198331625</v>
+        <v>17.43169198331626</v>
       </c>
       <c r="K18" t="n">
         <v>19.49127938002848</v>
       </c>
       <c r="L18" t="n">
-        <v>21.57498694628723</v>
+        <v>21.57498694628724</v>
       </c>
       <c r="M18" t="n">
-        <v>23.70306343020738</v>
+        <v>23.7030634302074</v>
       </c>
       <c r="N18" t="n">
-        <v>25.86420819260531</v>
+        <v>25.86420819260534</v>
       </c>
       <c r="O18" t="n">
-        <v>28.15757868541287</v>
+        <v>28.15757868541292</v>
       </c>
       <c r="P18" t="n">
-        <v>31.16438649804636</v>
+        <v>31.16438649804642</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.20553507491107</v>
+        <v>34.20553507491114</v>
       </c>
       <c r="R18" t="n">
         <v>34.37046665421315</v>
       </c>
       <c r="S18" t="n">
-        <v>33.79619534137248</v>
+        <v>33.7961953413725</v>
       </c>
       <c r="T18" t="n">
-        <v>33.28832322784392</v>
+        <v>33.28832322784396</v>
       </c>
       <c r="U18" t="n">
-        <v>32.84234602011588</v>
+        <v>32.84234602011587</v>
       </c>
       <c r="V18" t="n">
-        <v>32.45610333202447</v>
+        <v>32.45610333202448</v>
       </c>
       <c r="W18" t="n">
         <v>32.12600004132737</v>
@@ -2358,25 +2346,25 @@
         <v>31.60311252643768</v>
       </c>
       <c r="Z18" t="n">
-        <v>31.41375722191528</v>
+        <v>31.41375722191529</v>
       </c>
       <c r="AA18" t="n">
         <v>31.26183211983226</v>
       </c>
       <c r="AB18" t="n">
-        <v>31.13305924647298</v>
+        <v>31.13305924647297</v>
       </c>
       <c r="AC18" t="n">
         <v>31.00660016752023</v>
       </c>
       <c r="AD18" t="n">
-        <v>30.87914206381494</v>
+        <v>30.87914206381495</v>
       </c>
       <c r="AE18" t="n">
         <v>30.75106314331188</v>
       </c>
       <c r="AF18" t="n">
-        <v>30.62196831999215</v>
+        <v>30.62196831999212</v>
       </c>
       <c r="AG18" t="n">
         <v>30.49155064672551</v>
@@ -2385,7 +2373,7 @@
         <v>30.35911225998149</v>
       </c>
       <c r="AI18" t="n">
-        <v>30.22396195840452</v>
+        <v>30.22396195840447</v>
       </c>
     </row>
   </sheetData>
@@ -2403,509 +2391,509 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_0.00</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_0.97</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_1.94</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>t_2.91</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_3.88</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>t_4.85</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>t_5.82</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>t_6.79</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>t_7.76</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>t_8.73</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>t_9.70</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>t_10.67</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>t_11.64</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>t_12.61</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>t_13.58</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>t_14.55</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>t_15.52</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>t_16.48</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>t_17.45</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>t_18.42</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>t_19.39</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>t_20.36</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>t_21.33</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>t_22.30</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>t_23.27</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>t_24.24</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>t_25.21</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>t_26.18</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>t_27.15</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>t_28.12</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>t_29.09</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>t_30.06</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>t_31.03</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>t_32.00</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>t_32.97</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>t_33.94</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>t_34.91</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>t_35.88</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>t_36.85</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>t_37.82</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>t_38.79</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>t_39.76</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>t_40.73</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>t_41.70</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>t_42.67</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>t_43.64</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>t_44.61</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>t_45.58</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>t_46.55</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>t_47.52</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>t_48.48</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>t_49.45</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>t_50.42</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>t_51.39</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>t_52.36</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>t_53.33</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>t_54.30</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>t_55.27</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>t_56.24</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>t_57.21</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>t_58.18</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>t_59.15</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>t_60.12</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>t_61.09</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>t_62.06</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>t_63.03</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>t_64.00</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>t_64.97</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>t_65.94</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>t_66.91</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>t_67.88</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>t_68.85</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>t_69.82</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>t_70.79</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>t_71.76</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>t_72.73</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>t_73.70</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>t_74.67</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>t_75.64</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>t_76.61</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>t_77.58</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>t_78.55</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>t_79.52</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>t_80.48</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>t_81.45</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>t_82.42</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>t_83.39</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>t_84.36</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>t_85.33</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>t_86.30</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>t_87.27</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>t_88.24</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>t_89.21</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>t_90.18</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>t_91.15</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>t_92.12</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>t_93.09</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>t_94.06</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>t_95.03</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>t_96.00</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>dr_0.0000</t>
         </is>
@@ -3212,7 +3200,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>dr_0.0202</t>
         </is>
@@ -3519,7 +3507,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>dr_0.0404</t>
         </is>
@@ -3826,7 +3814,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dr_0.0606</t>
         </is>
@@ -4133,7 +4121,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>dr_0.0808</t>
         </is>
@@ -4440,7 +4428,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>dr_0.1010</t>
         </is>
@@ -4747,7 +4735,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>dr_0.1212</t>
         </is>
@@ -5054,7 +5042,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>dr_0.1414</t>
         </is>
@@ -5361,7 +5349,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>dr_0.1616</t>
         </is>
@@ -5668,7 +5656,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>dr_0.1818</t>
         </is>
@@ -5975,7 +5963,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>dr_0.2020</t>
         </is>
@@ -6282,7 +6270,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>dr_0.2222</t>
         </is>
@@ -6589,7 +6577,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>dr_0.2424</t>
         </is>
@@ -6896,7 +6884,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>dr_0.2626</t>
         </is>
@@ -7203,7 +7191,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>dr_0.2828</t>
         </is>
@@ -7510,7 +7498,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>dr_0.3030</t>
         </is>
@@ -7817,7 +7805,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>dr_0.3232</t>
         </is>
@@ -8124,7 +8112,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>dr_0.3434</t>
         </is>
@@ -8431,7 +8419,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>dr_0.3636</t>
         </is>
@@ -8738,7 +8726,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>dr_0.3838</t>
         </is>
@@ -9045,7 +9033,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>dr_0.4040</t>
         </is>
@@ -9352,7 +9340,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>dr_0.4242</t>
         </is>
@@ -9659,7 +9647,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>dr_0.4444</t>
         </is>
@@ -9966,7 +9954,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>dr_0.4646</t>
         </is>
@@ -10273,7 +10261,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>dr_0.4848</t>
         </is>
@@ -10580,7 +10568,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>dr_0.5051</t>
         </is>
@@ -10887,7 +10875,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>dr_0.5253</t>
         </is>
@@ -11194,7 +11182,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>dr_0.5455</t>
         </is>
@@ -11501,7 +11489,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>dr_0.5657</t>
         </is>
@@ -11808,7 +11796,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>dr_0.5859</t>
         </is>
@@ -12115,7 +12103,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>dr_0.6061</t>
         </is>
@@ -12422,7 +12410,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>dr_0.6263</t>
         </is>
@@ -12729,7 +12717,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>dr_0.6465</t>
         </is>
@@ -13036,7 +13024,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>dr_0.6667</t>
         </is>
@@ -13343,7 +13331,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>dr_0.6869</t>
         </is>
@@ -13650,7 +13638,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>dr_0.7071</t>
         </is>
@@ -13957,7 +13945,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>dr_0.7273</t>
         </is>
@@ -14264,7 +14252,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>dr_0.7475</t>
         </is>
@@ -14571,7 +14559,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>dr_0.7677</t>
         </is>
@@ -14878,7 +14866,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>dr_0.7879</t>
         </is>
@@ -15185,7 +15173,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>dr_0.8081</t>
         </is>
@@ -15492,7 +15480,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>dr_0.8283</t>
         </is>
@@ -15799,7 +15787,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>dr_0.8485</t>
         </is>
@@ -16106,7 +16094,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>dr_0.8687</t>
         </is>
@@ -16413,7 +16401,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>dr_0.8889</t>
         </is>
@@ -16720,7 +16708,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>dr_0.9091</t>
         </is>
@@ -17027,7 +17015,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>dr_0.9293</t>
         </is>
@@ -17334,7 +17322,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>dr_0.9495</t>
         </is>
@@ -17641,7 +17629,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>dr_0.9697</t>
         </is>
@@ -17948,7 +17936,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>dr_0.9899</t>
         </is>
@@ -18255,7 +18243,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>dr_1.0101</t>
         </is>
@@ -18562,7 +18550,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>dr_1.0303</t>
         </is>
@@ -18869,7 +18857,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>dr_1.0505</t>
         </is>
@@ -19176,7 +19164,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>dr_1.0707</t>
         </is>
@@ -19483,7 +19471,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>dr_1.0909</t>
         </is>
@@ -19790,7 +19778,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>dr_1.1111</t>
         </is>
@@ -20097,7 +20085,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>dr_1.1313</t>
         </is>
@@ -20404,7 +20392,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>dr_1.1515</t>
         </is>
@@ -20711,7 +20699,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>dr_1.1717</t>
         </is>
@@ -21018,7 +21006,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>dr_1.1919</t>
         </is>
@@ -21325,7 +21313,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>dr_1.2121</t>
         </is>
@@ -21632,7 +21620,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>dr_1.2323</t>
         </is>
@@ -21939,7 +21927,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>dr_1.2525</t>
         </is>
@@ -22246,7 +22234,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>dr_1.2727</t>
         </is>
@@ -22553,7 +22541,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>dr_1.2929</t>
         </is>
@@ -22860,7 +22848,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>dr_1.3131</t>
         </is>
@@ -23167,7 +23155,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>dr_1.3333</t>
         </is>
@@ -23474,7 +23462,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>dr_1.3535</t>
         </is>
@@ -23781,7 +23769,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>dr_1.3737</t>
         </is>
@@ -24088,7 +24076,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>dr_1.3939</t>
         </is>
@@ -24395,7 +24383,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>dr_1.4141</t>
         </is>
@@ -24702,7 +24690,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>dr_1.4343</t>
         </is>
@@ -25009,7 +24997,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>dr_1.4545</t>
         </is>
@@ -25316,7 +25304,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>dr_1.4747</t>
         </is>
@@ -25623,7 +25611,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>dr_1.4949</t>
         </is>
@@ -25930,7 +25918,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>dr_1.5152</t>
         </is>
@@ -26237,7 +26225,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>dr_1.5354</t>
         </is>
@@ -26544,7 +26532,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>dr_1.5556</t>
         </is>
@@ -26851,7 +26839,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>dr_1.5758</t>
         </is>
@@ -27158,7 +27146,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>dr_1.5960</t>
         </is>
@@ -27465,7 +27453,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>dr_1.6162</t>
         </is>
@@ -27772,7 +27760,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>dr_1.6364</t>
         </is>
@@ -28079,7 +28067,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>dr_1.6566</t>
         </is>
@@ -28386,7 +28374,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>dr_1.6768</t>
         </is>
@@ -28693,7 +28681,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>dr_1.6970</t>
         </is>
@@ -29000,7 +28988,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>dr_1.7172</t>
         </is>
@@ -29307,7 +29295,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>dr_1.7374</t>
         </is>
@@ -29614,7 +29602,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>dr_1.7576</t>
         </is>
@@ -29921,7 +29909,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>dr_1.7778</t>
         </is>
@@ -30228,7 +30216,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>dr_1.7980</t>
         </is>
@@ -30535,7 +30523,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>dr_1.8182</t>
         </is>
@@ -30842,7 +30830,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>dr_1.8384</t>
         </is>
@@ -31149,7 +31137,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>dr_1.8586</t>
         </is>
@@ -31456,7 +31444,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>dr_1.8788</t>
         </is>
@@ -31763,7 +31751,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>dr_1.8990</t>
         </is>
@@ -32070,7 +32058,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>dr_1.9192</t>
         </is>
@@ -32377,7 +32365,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>dr_1.9394</t>
         </is>
@@ -32684,7 +32672,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>dr_1.9596</t>
         </is>
@@ -32991,7 +32979,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>dr_1.9798</t>
         </is>
@@ -33298,7 +33286,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>dr_2.0000</t>
         </is>
@@ -33619,57 +33607,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>equation</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>drug</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>R0_O2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>E_stim_O2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>E_inhib_O2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EC50_stim_norm_O2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>IC50_norm_O2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n1_O2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>n2_O2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tau_stim_O2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tau_inhib_O2</t>
         </is>
@@ -33729,27 +33717,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Heatmap_Source</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Coefficient_Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -33758,12 +33746,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\Heatmaps\Mexiletine\O2_mean_sorted.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/Heatmaps/Mexiletine/O2_mean_sorted.csv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\EQN_Coefficients\all_equations_coefficients.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/EQN_Coefficients/all_equations_coefficients.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
